--- a/RoadRepair.Infrastructure/Reports/Blanks/MaterialsReport.xlsx
+++ b/RoadRepair.Infrastructure/Reports/Blanks/MaterialsReport.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
@@ -151,6 +151,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -563,6 +566,9 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
